--- a/data/trans_dic/P21B_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21B_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,24</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 16,47</t>
+          <t>4,08; 15,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,95</t>
+          <t>0,0; 30,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,75</t>
+          <t>0,0; 4,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,01</t>
+          <t>0,74; 5,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,87</t>
+          <t>2,01; 13,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 18,36</t>
+          <t>1,46; 14,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,8</t>
+          <t>0,43; 3,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,57</t>
+          <t>0,81; 4,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 11,49</t>
+          <t>4,31; 12,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 18,21</t>
+          <t>2,49; 16,74</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 10,35</t>
+          <t>1,73; 10,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,36</t>
+          <t>1,12; 6,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 18,43</t>
+          <t>5,18; 18,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,78</t>
+          <t>0,0; 9,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 9,67</t>
+          <t>2,37; 9,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 10,0</t>
+          <t>3,19; 10,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 17,47</t>
+          <t>6,76; 18,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 21,25</t>
+          <t>7,67; 20,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,47</t>
+          <t>3,0; 8,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,47</t>
+          <t>2,8; 7,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 15,62</t>
+          <t>7,46; 16,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 13,68</t>
+          <t>4,89; 13,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 9,49</t>
+          <t>0,75; 9,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 13,12</t>
+          <t>1,9; 13,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 17,72</t>
+          <t>5,84; 18,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,57</t>
+          <t>0,62; 5,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,44</t>
+          <t>0,53; 4,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 20,37</t>
+          <t>8,41; 20,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,89</t>
+          <t>3,62; 10,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,57</t>
+          <t>0,81; 4,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,23</t>
+          <t>0,76; 5,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 15,14</t>
+          <t>6,38; 14,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 12,13</t>
+          <t>5,59; 12,06</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 16,03</t>
+          <t>2,4; 16,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,65</t>
+          <t>1,04; 9,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 13,33</t>
+          <t>2,12; 14,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 14,13</t>
+          <t>5,04; 13,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 13,55</t>
+          <t>2,76; 13,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,68</t>
+          <t>1,03; 9,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 14,04</t>
+          <t>6,98; 14,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,66</t>
+          <t>1,06; 7,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 10,07</t>
+          <t>2,7; 9,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 8,95</t>
+          <t>2,19; 8,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 12,35</t>
+          <t>6,91; 12,7</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1277,52 +1277,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 21,49</t>
+          <t>3,29; 21,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,68</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,88</t>
+          <t>0,0; 10,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 11,84</t>
+          <t>3,11; 12,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,73</t>
+          <t>0,0; 9,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,01</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,11</t>
+          <t>0,0; 11,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 12,87</t>
+          <t>5,28; 13,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 11,3</t>
+          <t>2,53; 11,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,4</t>
+          <t>5,11; 10,52</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,16</t>
+          <t>0,0; 9,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,73; 21,3</t>
+          <t>6,36; 20,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,45</t>
+          <t>0,78; 7,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>0,0; 7,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,18</t>
+          <t>1,28; 11,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 7,54</t>
+          <t>3,16; 10,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,1</t>
+          <t>0,57; 5,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,0; 4,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,98</t>
+          <t>0,77; 7,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 10,09</t>
+          <t>5,77; 12,69</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,27</t>
+          <t>0,0; 13,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,52 +1567,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 20,28</t>
+          <t>2,06; 21,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 13,16</t>
+          <t>2,03; 12,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,15</t>
+          <t>1,14; 9,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,0</t>
+          <t>0,0; 10,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,13</t>
+          <t>1,45; 6,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,86</t>
+          <t>1,32; 8,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 9,25</t>
+          <t>1,8; 9,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,79</t>
+          <t>2,01; 6,87</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,27</t>
+          <t>2,59; 6,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,76</t>
+          <t>1,29; 3,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,34</t>
+          <t>4,74; 8,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,51</t>
+          <t>5,95; 10,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,31</t>
+          <t>1,93; 4,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,42</t>
+          <t>2,09; 4,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,42</t>
+          <t>5,27; 9,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,64</t>
+          <t>6,4; 9,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,5</t>
+          <t>2,49; 4,5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,76</t>
+          <t>2,08; 3,74</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,39</t>
+          <t>5,46; 8,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,4</t>
+          <t>6,6; 9,34</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>12820</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5149</t>
+          <t>0; 4963</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6406</t>
+          <t>0; 6789</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3976; 15242</t>
+          <t>3774; 14760</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 20447</t>
+          <t>0; 22405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6409</t>
+          <t>0; 5534</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>936; 7704</t>
+          <t>943; 7600</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1988; 11885</t>
+          <t>1855; 12362</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1560; 14942</t>
+          <t>1385; 14161</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>907; 7983</t>
+          <t>896; 7945</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1906; 10821</t>
+          <t>1910; 11060</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6894; 21248</t>
+          <t>7962; 22848</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4206; 28638</t>
+          <t>4202; 28241</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18366</t>
+          <t>18323</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2503; 11528</t>
+          <t>1925; 11406</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1831; 10379</t>
+          <t>1824; 10607</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4609; 17413</t>
+          <t>4899; 17555</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 11283</t>
+          <t>0; 9081</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4886; 17917</t>
+          <t>4385; 17622</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6987; 21242</t>
+          <t>6776; 21499</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9040; 24547</t>
+          <t>9500; 25301</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9503; 26081</t>
+          <t>10005; 26911</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8858; 25120</t>
+          <t>8906; 25031</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10733; 28055</t>
+          <t>10497; 28010</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16783; 36714</t>
+          <t>17527; 37683</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10096; 28870</t>
+          <t>11146; 30564</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12324</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20625</t>
+          <t>23619</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6204</t>
+          <t>0; 5978</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>894; 11842</t>
+          <t>942; 12175</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2627; 13842</t>
+          <t>2000; 14726</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6507; 20791</t>
+          <t>7511; 23153</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>839; 7641</t>
+          <t>850; 8077</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>878; 7470</t>
+          <t>899; 7430</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11082; 28971</t>
+          <t>11954; 28882</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4607; 14211</t>
+          <t>5458; 15923</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1014; 10309</t>
+          <t>1829; 9870</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2762; 15321</t>
+          <t>2213; 15283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16442; 37504</t>
+          <t>15813; 36197</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13231; 30077</t>
+          <t>15640; 33715</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15851</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29929</t>
+          <t>33299</t>
         </is>
       </c>
     </row>
@@ -2692,22 +2692,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1991; 12689</t>
+          <t>1901; 12728</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1011; 10532</t>
+          <t>1028; 9726</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1107; 11887</t>
+          <t>1891; 13356</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7905; 22352</t>
+          <t>8727; 22801</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2717,37 +2717,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3134; 17591</t>
+          <t>3578; 17036</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1103; 10791</t>
+          <t>1153; 10460</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10806; 22745</t>
+          <t>12338; 25377</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1877; 12189</t>
+          <t>1933; 13051</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6472; 23033</t>
+          <t>6185; 22628</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4295; 17953</t>
+          <t>4403; 17767</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21475; 39543</t>
+          <t>24175; 44461</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>20675</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2064; 13558</t>
+          <t>2079; 13685</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4979</t>
+          <t>0; 5002</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7408</t>
+          <t>0; 7187</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3168; 13565</t>
+          <t>3869; 15197</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8408</t>
+          <t>0; 8404</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5217</t>
+          <t>0; 5476</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 10758</t>
+          <t>0; 10262</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6947; 16852</t>
+          <t>7748; 19391</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3616; 16900</t>
+          <t>3782; 16712</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 7063</t>
+          <t>0; 6968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1216; 13344</t>
+          <t>1202; 13338</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13293; 27993</t>
+          <t>13858; 28522</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>15290</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4131</t>
+          <t>0; 4878</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3118,52 +3118,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5220</t>
+          <t>0; 5137</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4308; 13644</t>
+          <t>4572; 15066</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>734; 7054</t>
+          <t>734; 7104</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5858</t>
+          <t>0; 6692</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>996; 8608</t>
+          <t>984; 8697</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>910; 22358</t>
+          <t>3225; 10710</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>893; 7960</t>
+          <t>891; 7932</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 6338</t>
+          <t>0; 6767</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1071; 9346</t>
+          <t>1027; 10228</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2742; 36366</t>
+          <t>10037; 22081</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7460</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6948</t>
+          <t>0; 7623</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3326,52 +3326,52 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>939; 9063</t>
+          <t>922; 9456</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1271; 7623</t>
+          <t>1287; 7701</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1191; 10667</t>
+          <t>1201; 10197</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5233</t>
+          <t>0; 5622</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 7758</t>
+          <t>0; 9740</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1574; 8718</t>
+          <t>1920; 8670</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2011; 12713</t>
+          <t>2143; 13603</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 5222</t>
+          <t>0; 6206</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2225; 13107</t>
+          <t>2548; 14108</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3742; 12241</t>
+          <t>3934; 13454</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53665</t>
+          <t>57833</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>66627</t>
+          <t>73654</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>120292</t>
+          <t>131486</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15263; 35006</t>
+          <t>14448; 35954</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9291; 26442</t>
+          <t>9048; 25751</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26552; 51514</t>
+          <t>26160; 49407</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>39799; 71077</t>
+          <t>43599; 79154</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15672; 35543</t>
+          <t>15880; 35103</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20624; 43213</t>
+          <t>20445; 44572</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39491; 70597</t>
+          <t>39470; 71959</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>35499; 90445</t>
+          <t>59838; 90891</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33647; 62143</t>
+          <t>34462; 62244</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>34503; 63203</t>
+          <t>35008; 62867</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>71145; 109142</t>
+          <t>70960; 109790</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>79066; 144678</t>
+          <t>110035; 155707</t>
         </is>
       </c>
     </row>
